--- a/output/pdf_financials_xlsx/RSM.xlsx
+++ b/output/pdf_financials_xlsx/RSM.xlsx
@@ -1129,13 +1129,13 @@
         <v>-0.073448</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.748928</v>
+        <v>-0.748928</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.465484</v>
+        <v>-4.465484</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.700373</v>
+        <v>-3.700373</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-6.288396</v>
@@ -1365,13 +1365,13 @@
         <v>-0.073448</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.748928</v>
+        <v>-0.748928</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.465484</v>
+        <v>-4.465484</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.700373</v>
+        <v>-3.700373</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-6.288396</v>
@@ -1503,13 +1503,13 @@
         <v>-0.073448</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.748928</v>
+        <v>-0.748928</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.465484</v>
+        <v>-4.465484</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.700373</v>
+        <v>-3.700373</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-6.288396</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-44.65484</v>
+        <v>44.65484</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-61.672883</v>
+        <v>61.672883</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>89.83422899999999</v>
@@ -1707,13 +1707,13 @@
         <v>-0.073448</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.748928</v>
+        <v>-0.748928</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>4.465484</v>
+        <v>-4.465484</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.700373</v>
+        <v>-3.700373</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-6.288396</v>
@@ -1799,13 +1799,13 @@
         <v>-0.073448</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.749019</v>
+        <v>-0.748837</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.466693</v>
+        <v>-4.464275</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.703668</v>
+        <v>-3.697078</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-6.242693</v>
@@ -1917,13 +1917,13 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -4791,22 +4791,22 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.025982</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.06474299999999999</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>0.032087</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>0.032087</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>0.032087</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>0.032087</v>
       </c>
     </row>
     <row r="92">
@@ -5137,7 +5137,7 @@
         <v>-0.073448</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.748928</v>
+        <v>-0.748928</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-4.465484</v>
@@ -8209,7 +8209,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -24645,10 +24649,10 @@
         </is>
       </c>
       <c r="N223" s="5" t="n">
-        <v>4.465484</v>
+        <v>-4.465484</v>
       </c>
       <c r="O223" s="5" t="n">
-        <v>3.700373</v>
+        <v>-3.700373</v>
       </c>
       <c r="P223" t="inlineStr">
         <is>
@@ -25448,10 +25452,10 @@
         </is>
       </c>
       <c r="M233" s="5" t="n">
-        <v>0.748928</v>
+        <v>-0.748928</v>
       </c>
       <c r="N233" s="5" t="n">
-        <v>4.465484</v>
+        <v>-4.465484</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -25531,10 +25535,10 @@
         </is>
       </c>
       <c r="M234" s="5" t="n">
-        <v>0.839653</v>
+        <v>-0.839653</v>
       </c>
       <c r="N234" s="5" t="n">
-        <v>4.432828</v>
+        <v>-4.432828</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RSM.xlsx
+++ b/output/pdf_financials_xlsx/RSM.xlsx
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000265</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -933,31 +933,31 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007781</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008045999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.006941</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.006297</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007405</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012025</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.171575</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.059185</v>
       </c>
     </row>
     <row r="13">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.090336</v>
+        <v>-0.090601</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.088558</v>
@@ -1695,31 +1695,31 @@
         <v>-0.188889</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.060847</v>
+        <v>-0.06862799999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.044601</v>
+        <v>-0.052647</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.137786</v>
+        <v>-0.144727</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.073448</v>
+        <v>-0.079745</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.748928</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.465484</v>
+        <v>-4.458079</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.700373</v>
+        <v>-3.688348</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.288396</v>
+        <v>-6.116821</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.035643</v>
+        <v>-3.976458</v>
       </c>
     </row>
     <row r="28">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.090336</v>
+        <v>-0.090601</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.088558</v>
@@ -1787,31 +1787,31 @@
         <v>-0.188889</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.060847</v>
+        <v>-0.06862799999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.044601</v>
+        <v>-0.052647</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.137786</v>
+        <v>-0.144727</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.073448</v>
+        <v>-0.079745</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.748837</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.464275</v>
+        <v>-4.45687</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.697078</v>
+        <v>-3.685053</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.242693</v>
+        <v>-6.071118</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.99877</v>
+        <v>-3.939585</v>
       </c>
     </row>
     <row r="30">
@@ -2018,43 +2018,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002557</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.0009700000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000628</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.852901</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.792992</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.745254</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.613283</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.013058</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009469999999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006759</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.921272</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.843664</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.091663</v>
       </c>
     </row>
     <row r="35">
@@ -2110,43 +2110,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002557</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.0009700000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000628</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.852901</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.792992</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.745254</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.613283</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.013058</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.009469999999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.006759</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.921272</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.843664</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.091663</v>
       </c>
     </row>
     <row r="37">
@@ -2662,43 +2662,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002557</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.0009700000000000001</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001045</v>
+        <v>0.000417</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.860198</v>
+        <v>0.007297</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.798747</v>
+        <v>0.005755</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.751009</v>
+        <v>0.005755</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.615418</v>
+        <v>0.002135</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.013028</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009469999999999999</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.010658</v>
+        <v>0.003899</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.944282</v>
+        <v>0.02301</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.898622</v>
+        <v>0.054958</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.162529</v>
+        <v>0.070866</v>
       </c>
     </row>
     <row r="49">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -26115,7 +26115,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -27114,7 +27114,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -29299,7 +29299,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">

--- a/output/pdf_financials_xlsx/RSM.xlsx
+++ b/output/pdf_financials_xlsx/RSM.xlsx
@@ -1759,13 +1759,13 @@
         <v>0.001209</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.003295</v>
+        <v>0.011985</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.045703</v>
+        <v>0.029326</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.036873</v>
+        <v>0.007247</v>
       </c>
     </row>
     <row r="29">
@@ -1805,13 +1805,13 @@
         <v>-4.45687</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.685053</v>
+        <v>-3.676363</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.071118</v>
+        <v>-6.087495</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.939585</v>
+        <v>-3.969211</v>
       </c>
     </row>
     <row r="30">
@@ -5189,13 +5189,13 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.011985</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.029326</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.007247</v>
       </c>
     </row>
     <row r="101">
@@ -13175,7 +13175,11 @@
           <t>Depreciation of right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -17645,7 +17649,11 @@
           <t>Depreciation of right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -22953,7 +22961,11 @@
           <t>Depreciation of right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -24357,7 +24369,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RSM.xlsx
+++ b/output/pdf_financials_xlsx/RSM.xlsx
@@ -3455,25 +3455,25 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.050236</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.033082</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.001736</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.000359</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.000177</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.004836</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.014709</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -3593,40 +3593,40 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.00818</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.009169999999999999</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.008175</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.022233</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.613357</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.06776799999999999</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.070796</v>
       </c>
     </row>
     <row r="68">
@@ -5217,16 +5217,16 @@
         <v>0.0005509999999999999</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000976</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.000575</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001469</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.00184</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.026707</v>
@@ -5447,16 +5447,16 @@
         <v>-0.019112</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.001914</v>
+        <v>0.000938</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.003712</v>
+        <v>-0.003137</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.007284</v>
+        <v>0.005815</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.011833</v>
+        <v>0.013673</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>0.421737</v>
@@ -14433,7 +14433,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -18461,7 +18465,11 @@
           <t>Private placement 7</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -18779,7 +18787,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -19561,7 +19573,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
